--- a/generated/delta-crown-owner-decision-workbook.xlsx
+++ b/generated/delta-crown-owner-decision-workbook.xlsx
@@ -1,51 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="Decision Matrix" sheetId="2" r:id="rId2"/>
-    <sheet name="Action Tracker" sheetId="3" r:id="rId3"/>
-    <sheet name="Evidence" sheetId="4" r:id="rId4"/>
-    <sheet name="Glossary" sheetId="5" r:id="rId5"/>
-    <sheet name="OD-001" sheetId="6" r:id="rId6"/>
-    <sheet name="OD-002" sheetId="7" r:id="rId7"/>
-    <sheet name="OD-003" sheetId="8" r:id="rId8"/>
-    <sheet name="OD-004" sheetId="9" r:id="rId9"/>
-    <sheet name="OD-005" sheetId="10" r:id="rId10"/>
-    <sheet name="OD-006" sheetId="11" r:id="rId11"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Decision Matrix" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Action Tracker" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Evidence" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Glossary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OD-001" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="OD-002" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="OD-003" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="OD-004" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="OD-005" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="OD-006" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <name val="Aptos"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="000B3D3D"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
       <sz val="11"/>
+    </font>
+    <font>
       <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F1F1F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000B3D3D"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B3D3D"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="000B3D3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,3717 +91,5014 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DashboardTable" displayName="DashboardTable" ref="A4:C9" headerRowCount="1">
+  <autoFilter ref="A4:C9"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Metric"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Why it matters"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="OD003Overview" displayName="OD003Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="OD003Options" displayName="OD003Options" ref="A14:D17" headerRowCount="1">
+  <autoFilter ref="A14:D17"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="OD004Overview" displayName="OD004Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="OD004Options" displayName="OD004Options" ref="A14:D18" headerRowCount="1">
+  <autoFilter ref="A14:D18"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="OD005Overview" displayName="OD005Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="OD005Options" displayName="OD005Options" ref="A14:D17" headerRowCount="1">
+  <autoFilter ref="A14:D17"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="OD006Overview" displayName="OD006Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="OD006Options" displayName="OD006Options" ref="A14:D18" headerRowCount="1">
+  <autoFilter ref="A14:D18"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DecisionMatrix" displayName="DecisionMatrix" ref="A4:I10" headerRowCount="1">
+  <autoFilter ref="A4:I10"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Decision"/>
+    <tableColumn id="3" name="Current state"/>
+    <tableColumn id="4" name="Risk"/>
+    <tableColumn id="5" name="Recommendation"/>
+    <tableColumn id="6" name="Owner needed"/>
+    <tableColumn id="7" name="Tyler decision"/>
+    <tableColumn id="8" name="Decision date"/>
+    <tableColumn id="9" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ActionTracker" displayName="ActionTracker" ref="A4:G22" headerRowCount="1">
+  <autoFilter ref="A4:G22"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Decision ID"/>
+    <tableColumn id="2" name="Follow-up action"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="Status"/>
+    <tableColumn id="6" name="Target date"/>
+    <tableColumn id="7" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceTable" displayName="EvidenceTable" ref="A4:C23" headerRowCount="1">
+  <autoFilter ref="A4:C23"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Decision ID"/>
+    <tableColumn id="2" name="Evidence"/>
+    <tableColumn id="3" name="Source / context"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="GlossaryTable" displayName="GlossaryTable" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Term"/>
+    <tableColumn id="2" name="Meaning"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="OD001Overview" displayName="OD001Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OD001Options" displayName="OD001Options" ref="A14:D17" headerRowCount="1">
+  <autoFilter ref="A14:D17"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="OD002Overview" displayName="OD002Overview" ref="A4:B11" headerRowCount="1">
+  <autoFilter ref="A4:B11"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Detail"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="OD002Options" displayName="OD002Options" ref="A14:D18" headerRowCount="1">
+  <autoFilter ref="A14:D18"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Option"/>
+    <tableColumn id="2" name="Description"/>
+    <tableColumn id="3" name="Pros"/>
+    <tableColumn id="4" name="Cons"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Delta Crown Owner Decision Workbook</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Launch-blocking owner decisions, recommendations, evidence, and follow-up actions</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Workbook purpose</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Owner launch decisions</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converts remaining launch blockers into explicit choices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Decisions</t>
-        </is>
-      </c>
-      <c r="B3">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Converts launch blockers into explicit choices.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Decision count</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Six decisions block full production-launch claims.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Six decisions currently block full production-launch claims.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommended launch posture</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Controlled pilot / owner validation</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full launch still needs decisions and Teams channel evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Built and hardened, but not full production launch yet.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Top technical blocker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Teams channel read context</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Members are readable; team/channel detail still blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Members readable; team/channel detail still blocked.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Top governance blocker</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Named owners + DLP posture</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Production claims need accountable owners and enforcement decisions.</t>
-        </is>
-      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Needs accountable owners and enforcement decisions.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>1. Start on Decision Matrix and pick a Tyler decision for each row.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2. Use OD-001 through OD-006 tabs for evidence, risks, options, and recommendation detail.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>3. Use Action Tracker to split approved work into small follow-up change issues.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>4. Do not make tenant-impacting changes from this workbook alone; create tracked change issues first.</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-005 — DeltaCrown-TeamsProvisioner-TEMP app fate</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-005</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DeltaCrown-TeamsProvisioner-TEMP app fate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>TEMP app registration exists with three password credentials expired on 2026-04-16.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Expired temporary apps are security/governance clutter unless dependency and owner are documented.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Delete the app if no dependency remains. Otherwise rename/document owner and remove expired secrets.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler / tenant app owner</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Delete app after dependency check.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Cleanest if no longer used.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Requires confidence no automation depends on it.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Keep, rename, assign owner, remove expired credentials, document purpose.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Safe if still needed.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Keeps extra app surface.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Keep as-is temporarily with deadline.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Buys time.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Still leaves known smell.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-security-apps-licenses-inventory-summary.md lists DeltaCrown-TeamsProvisioner-TEMP.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Inventory found three expired app password credentials for the TEMP app.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Safety notes say not to delete app registrations without dependency review and approval.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Confirm whether any Teams provisioning automation still uses the app.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Create cleanup issue for delete or rename/credential cleanup.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Verify app inventory after cleanup.</t>
         </is>
       </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-006 — ClientServices deprecation banner / cleanup</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ClientServices deprecation banner / cleanup</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Legacy ClientServices artifacts are documented as empty/broad and client records are out of M365 scope.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Users may treat old ClientServices resources as approved client-data storage, conflicting with current scope.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Add a visible deprecation/owner note first. Do not delete, rename, or repurpose until owner approval and cleanup plan exist.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler + data/content owner</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Add deprecation/banner notice: do not use for client records; pending cleanup.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Immediate clear signal without destructive changes.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Requires tenant page/banner edit.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Remove navigation links only.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Reduces accidental use.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Does not explain what happened.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Archive or delete after owner approval.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Cleaner long-term.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Unsafe before dependency/content approval.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Repurpose as Brand Resources after approval.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>May reuse existing resource.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Risky URL/history/permission baggage.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>docs/legacy-clientservices-cleanup-register.md states ClientServices/client-record assumptions are legacy.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-sharepoint-pnp-inventory-summary.md documents ClientServices artifacts and permissions metadata.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Brand Resources target model says client records are out of Microsoft 365 scope.</t>
         </is>
       </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Approve banner wording.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Create tenant change issue for non-destructive deprecation signal.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Decide later: archive, replace, repurpose, or remove.</t>
         </is>
       </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Decision Matrix</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>One-line view of what Tyler/Megan need to decide</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Tyler decision</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Decision date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>GitHub default branch / stale main</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Remote default branch is main; canonical current project work and GitHub Pages source are on gh-pages.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Future operators may land on stale architecture and treat it as current.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Prefer changing GitHub default branch to gh-pages. If that is not possible, make main a hard redirect/archive branch.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Tyler / repo owner</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Brand Resources vs Brand Assets model</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Docs target Brand Resources; tenant/docs still include Marketing Brand Assets and legacy ClientServices artifacts.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Users and MSP operators may confuse reference material, marketing execution assets, legacy ClientServices, and client records.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Use Brand Resources as the staff-facing reference concept; keep Brand Assets as Marketing execution/library if needed. Do not repurpose ClientServices yet.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Tyler + business/content owner</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Dynamic security group owners</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>AllStaff, Managers, Marketing, Stylists, and External have zero owners in Graph.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Nobody is clearly accountable when metadata, membership, or access drifts.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Assign at least two owners per group: MSP/operator plus business/access owner.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Tyler / Megan</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>DLP test mode vs enforce path</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>DCE-Data-Protection and Corp-Data-Protection are TestWithNotifications; External-Sharing-Block is enabled.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Test mode is not final enforcement. Claims about production DLP must distinguish test from enforce.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Review raw DLP rule details, then choose a staged enforce flip unless rule review proves very low risk.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Tyler + security/compliance owner</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>DeltaCrown-TeamsProvisioner-TEMP app fate</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>TEMP app registration exists with three password credentials expired on 2026-04-16.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Expired temporary apps are security/governance clutter unless dependency and owner are documented.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Delete the app if no dependency remains. Otherwise rename/document owner and remove expired secrets.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Tyler / tenant app owner</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>ClientServices deprecation banner / cleanup</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Legacy ClientServices artifacts are documented as empty/broad and client records are out of M365 scope.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Users may treat old ClientServices resources as approved client-data storage, conflicting with current scope.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Add a visible deprecation/owner note first. Do not delete, rename, or repurpose until owner approval and cleanup plan exist.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Tyler + data/content owner</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Action Tracker</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Follow-up actions after decisions are approved</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Decision ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Follow-up action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Target date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>If A: update GitHub repository default branch setting.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Tyler / repo owner</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>If B: patch main README to point to gh-pages and warn it is legacy.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Tyler / repo owner</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>If C: tag legacy main, verify no workflows depend on it, then archive/delete.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Tyler / repo owner</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Approve final vocabulary.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Tyler + business/content owner</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Create follow-up Brand Resources implementation issue after decision.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Tyler + business/content owner</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Do not rename/delete/repurpose live ClientServices resources yet.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Tyler + business/content owner</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Name owner candidates for each group.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Tyler / Megan</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Create tenant change issue for owner assignment.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Tyler / Megan</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Verify owner assignment via Graph after change.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Tyler / Megan</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Review local raw DLP rule exports.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Tyler + security/compliance owner</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Pick enforce order and maintenance window.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Tyler + security/compliance owner</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Create change issue with rollback owner and validation plan.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Tyler + security/compliance owner</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Confirm whether any Teams provisioning automation still uses the app.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Tyler / tenant app owner</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Create cleanup issue for delete or rename/credential cleanup.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Tyler / tenant app owner</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Verify app inventory after cleanup.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Tyler / tenant app owner</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Approve banner wording.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Tyler + data/content owner</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Create tenant change issue for non-destructive deprecation signal.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Tyler + data/content owner</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Decide later: archive, replace, repurpose, or remove.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Tyler + data/content owner</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Supporting evidence behind recommendations</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Decision ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Source / context</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>git remote show origin reports HEAD branch: main.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>README says gh-pages is canonical and main is abandoned earlier architecture.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>OD-001</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Live public site publishes from gh-pages.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>docs/brand-resources-target-model.md defines Brand Resources as reusable reference material, not CRM/client records.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>docs/clientservices-to-brand-resources-transition-plan.md says ClientServices assumptions are legacy.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>OD-002</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>docs/legacy-clientservices-cleanup-register.md prohibits tenant cleanup without inventory and approval.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-identity-inventory-summary.md shows zero owners for all five dynamic groups.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Current group counts: AllStaff=6, Managers=1, Marketing=0, Stylists=0, External=0.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>OD-003</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Production launch readiness report marks named operational owners as a no-go item.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-compliance-inventory-summary.md lists 6 DLP policies and 8 rules.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>DCE-Data-Protection mode: TestWithNotifications.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Corp-Data-Protection mode: TestWithNotifications.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>OD-004</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>External-Sharing-Block mode: Enable.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-security-apps-licenses-inventory-summary.md lists DeltaCrown-TeamsProvisioner-TEMP.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Inventory found three expired app password credentials for the TEMP app.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>OD-005</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Safety notes say not to delete app registrations without dependency review and approval.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>docs/legacy-clientservices-cleanup-register.md states ClientServices/client-record assumptions are legacy.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-sharepoint-pnp-inventory-summary.md documents ClientServices artifacts and permissions metadata.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>OD-006</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Brand Resources target model says client records are out of Microsoft 365 scope.</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>See repo docs referenced in owner-decision worksheet.</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>See repo docs and owner-decision worksheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Glossary</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Plain-English definitions for decision terms</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>DDG</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Dynamic Distribution Group for Exchange mail routing.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Dynamic security group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Entra group whose membership is calculated from user attributes.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>TestWithNotifications</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>DLP policy mode that warns/tests without full enforcement.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Brand Resources</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Approved staff-facing reference material, not client records.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Brand Assets</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Marketing execution/asset library concept.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ClientServices</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Legacy concept/artifacts; not approved client-record storage in M365.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Controlled pilot</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Limited validation state before full launch approval.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-001 — GitHub default branch / stale main</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GitHub default branch / stale main</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Remote default branch is main; canonical current project work and GitHub Pages source are on gh-pages.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Future operators may land on stale architecture and treat it as current.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Prefer changing GitHub default branch to gh-pages. If that is not possible, make main a hard redirect/archive branch.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler / repo owner</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Change GitHub default branch to gh-pages.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Repo landing page matches current work.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Requires GitHub repo admin action.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Keep main but replace README with a clear redirect to gh-pages.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Fast and low risk.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Users can still browse stale files.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Archive/delete stale main after preservation tag.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Cleanest long-term.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Higher governance risk; needs explicit approval.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>git remote show origin reports HEAD branch: main.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>README says gh-pages is canonical and main is abandoned earlier architecture.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Live public site publishes from gh-pages.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>If A: update GitHub repository default branch setting.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>If B: patch main README to point to gh-pages and warn it is legacy.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>If C: tag legacy main, verify no workflows depend on it, then archive/delete.</t>
         </is>
       </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-002 — Brand Resources vs Brand Assets model</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-002</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brand Resources vs Brand Assets model</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Docs target Brand Resources; tenant/docs still include Marketing Brand Assets and legacy ClientServices artifacts.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Users and MSP operators may confuse reference material, marketing execution assets, legacy ClientServices, and client records.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Use Brand Resources as the staff-facing reference concept; keep Brand Assets as Marketing execution/library if needed. Do not repurpose ClientServices yet.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler + business/content owner</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Brand Resources = staff reference; Brand Assets = Marketing execution library.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Clear separation of audience and purpose.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Requires explaining two related terms.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Consolidate everything to Brand Resources.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Simplest user-facing label.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Unsafe before dependency/content review.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Keep Brand Assets as the only user-facing term.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Matches current Marketing wording.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Weakens replacement of ClientServices assumptions.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Defer until owners classify current usage.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Avoids premature naming decision.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Slows launch cleanup.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>docs/brand-resources-target-model.md defines Brand Resources as reusable reference material, not CRM/client records.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>docs/clientservices-to-brand-resources-transition-plan.md says ClientServices assumptions are legacy.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>docs/legacy-clientservices-cleanup-register.md prohibits tenant cleanup without inventory and approval.</t>
         </is>
       </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Approve final vocabulary.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Create follow-up Brand Resources implementation issue after decision.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Do not rename/delete/repurpose live ClientServices resources yet.</t>
         </is>
       </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-003 — Dynamic security group owners</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-003</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dynamic security group owners</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>AllStaff, Managers, Marketing, Stylists, and External have zero owners in Graph.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Nobody is clearly accountable when metadata, membership, or access drifts.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Assign at least two owners per group: MSP/operator plus business/access owner.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler / Megan</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Two owners per group: MSP operator + business/access owner.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Best production governance.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Requires naming humans now.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>One central identity owner for all dynamic groups.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Fastest owner assignment.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Weak business accountability.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Keep ownerless until metadata cleanup finishes.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Avoids churn.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Leaves governance gap open.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-identity-inventory-summary.md shows zero owners for all five dynamic groups.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Current group counts: AllStaff=6, Managers=1, Marketing=0, Stylists=0, External=0.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Production launch readiness report marks named operational owners as a no-go item.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Name owner candidates for each group.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Create tenant change issue for owner assignment.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Verify owner assignment via Graph after change.</t>
         </is>
       </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>OD-004 — DLP test mode vs enforce path</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Decision detail, options, evidence, and action prompts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Decision ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OD-004</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DLP test mode vs enforce path</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Current state</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>DCE-Data-Protection and Corp-Data-Protection are TestWithNotifications; External-Sharing-Block is enabled.</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Test mode is not final enforcement. Claims about production DLP must distinguish test from enforce.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Review raw DLP rule details, then choose a staged enforce flip unless rule review proves very low risk.</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Owner needed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tyler + security/compliance owner</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Tyler selected option</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Approval / date</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Follow-up issue</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Pros</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Cons</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Keep test mode for 30 days and review alerts.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Lower business disruption risk.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Not fully enforcing.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Flip both policies to enforce in one window.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Fastest enforcement posture.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Higher false-positive risk.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Enforce one policy first, then the other.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Balanced staged rollout.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Takes longer.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Keep test mode indefinitely.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Avoids disruption.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Not production-grade.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Supporting evidence</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>docs/delta-crown-compliance-inventory-summary.md lists 6 DLP policies and 8 rules.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>DCE-Data-Protection mode: TestWithNotifications.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Corp-Data-Protection mode: TestWithNotifications.</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>External-Sharing-Block mode: Enable.</t>
         </is>
       </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Follow-up actions</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Review local raw DLP rule exports.</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Pick enforce order and maintenance window.</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Create change issue with rollback owner and validation plan.</t>
         </is>
       </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>